--- a/output/pdf_financials_xlsx/ZOG.X.xlsx
+++ b/output/pdf_financials_xlsx/ZOG.X.xlsx
@@ -2356,13 +2356,13 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.921911</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.921911</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.936611</v>
       </c>
     </row>
     <row r="93">
@@ -3600,7 +3600,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3892,7 +3896,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -4474,7 +4482,11 @@
           <t>Reserves 12 1,921,911</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ZOG.X.xlsx
+++ b/output/pdf_financials_xlsx/ZOG.X.xlsx
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000245</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000539</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-5.706734</v>
+        <v>-5.706979</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.425359</v>
+        <v>-0.425898</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.040561</v>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.706734</v>
+        <v>-5.706979</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.425359</v>
+        <v>-0.425898</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.040561</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.039724</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.002263</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.014218</v>
       </c>
     </row>
     <row r="35">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.039724</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.002263</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.014218</v>
       </c>
     </row>
     <row r="37">
@@ -1403,10 +1403,10 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.002263</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.019808</v>
+        <v>0.00559</v>
       </c>
     </row>
     <row r="49">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">

--- a/output/pdf_financials_xlsx/ZOG.X.xlsx
+++ b/output/pdf_financials_xlsx/ZOG.X.xlsx
@@ -1811,19 +1811,17 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.446148</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.036382</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="68">
@@ -2708,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.001255</v>
       </c>
     </row>
     <row r="111">
@@ -4696,7 +4694,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -5046,7 +5048,11 @@
           <t>Net proceeds from issuance of private placement</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -5650,7 +5656,11 @@
           <t>Net proceeds from issuance of private placement 12</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>0.06</v>
       </c>
